--- a/esyluban/examples/dev/DataTables/test/global.xlsx
+++ b/esyluban/examples/dev/DataTables/test/global.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestGlobal" &amp; value_type="test.TestGlobal" &amp; mode="one" &amp; read_schema_from_file="false" &amp; input="test/global.xlsx" &amp; output="test_tbtestglobal"</t>
+          <t>full_name="test.TbTestGlobal" &amp; mode="one" &amp; input="test/global.xlsx"</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       <c r="D2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
